--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19115" windowHeight="10860" firstSheet="4" activeTab="9"/>
+    <workbookView windowWidth="19115" windowHeight="10860" firstSheet="4" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="75">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -178,6 +178,27 @@
   </si>
   <si>
     <t>台版双美/肤莱美 肤力原</t>
+  </si>
+  <si>
+    <t>悦白之几/3型</t>
+  </si>
+  <si>
+    <t>3ml*5瓶/盒</t>
+  </si>
+  <si>
+    <t>悦白之几/17型</t>
+  </si>
+  <si>
+    <t>悦白之几/韵镜</t>
+  </si>
+  <si>
+    <t>16mg/瓶/盒</t>
+  </si>
+  <si>
+    <t>悦白之几/即境</t>
+  </si>
+  <si>
+    <t>5mg*5瓶/盒</t>
   </si>
   <si>
     <t>伊妍仕(欧版）/ELLANSE--M</t>
@@ -3989,10 +4010,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C2" s="2">
         <v>470</v>
@@ -4003,10 +4024,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C3" s="2">
         <v>180</v>
@@ -4017,10 +4038,10 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C4" s="2">
         <v>840</v>
@@ -4031,10 +4052,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C5" s="2">
         <v>3000</v>
@@ -4045,10 +4066,10 @@
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C6" s="2">
         <v>380</v>
@@ -4059,10 +4080,10 @@
     </row>
     <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C7" s="2">
         <v>290</v>
@@ -4073,10 +4094,10 @@
     </row>
     <row r="8" ht="22.05" customHeight="1" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C8" s="2">
         <v>330</v>
@@ -4197,37 +4218,37 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -5718,8 +5739,8 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="3"/>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -5821,6 +5842,62 @@
       </c>
       <c r="D7" s="2">
         <v>1590</v>
+      </c>
+    </row>
+    <row r="8" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1350</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="9" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="2">
+        <v>620</v>
+      </c>
+      <c r="D9" s="2">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="10" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="2">
+        <v>735</v>
+      </c>
+      <c r="D10" s="2">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="11" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="2">
+        <v>780</v>
+      </c>
+      <c r="D11" s="2">
+        <v>780</v>
       </c>
     </row>
   </sheetData>
@@ -5885,7 +5962,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>5</v>
@@ -5899,7 +5976,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>5</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19115" windowHeight="10860" firstSheet="4" activeTab="6"/>
+    <workbookView windowWidth="19115" windowHeight="10860" firstSheet="4"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -22,138 +22,522 @@
     <sheet name="医用敷贴" sheetId="14" r:id="rId13"/>
     <sheet name="删除" sheetId="15" r:id="rId14"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83">
+  <si>
+    <r>
+      <t>品牌/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>型号</t>
+    </r>
+  </si>
+  <si>
+    <t>规格</t>
+  </si>
+  <si>
+    <t>昨日价格</t>
+  </si>
+  <si>
+    <t>今日价格</t>
+  </si>
+  <si>
+    <r>
+      <t>乔雅登（韩版）/5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>号</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>丰颜</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1ml*2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>支</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>盒</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>乔雅登（韩版）/6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>号</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>朔颜</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>乔雅登（韩版）/7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>号</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>缇颜</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>乔雅登（韩版）/8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>号</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>质颜</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>瑞蓝（欧版）/2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>号</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1ml/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>支</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>盒</t>
+    </r>
+  </si>
+  <si>
+    <t>¥580</t>
+  </si>
+  <si>
+    <r>
+      <t>瑞蓝（欧版）/3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>号</t>
+    </r>
+  </si>
+  <si>
+    <t>¥620</t>
+  </si>
+  <si>
+    <r>
+      <t>瑞蓝（欧版）/4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>号</t>
+    </r>
+  </si>
+  <si>
+    <t>¥640</t>
+  </si>
+  <si>
+    <r>
+      <t>瑞蓝（欧版）/5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>号</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>瑞蓝（欧版）/6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>号</t>
+    </r>
+  </si>
+  <si>
+    <t>瑞蓝（欧版）/refyne</t>
+  </si>
+  <si>
+    <r>
+      <t>瑞蓝（欧版）/Kysse</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>唇部</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">姣兰 / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>经典玻尿酸</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">姣兰 / Lips </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>唇部玻尿酸</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>艾莉薇（韩版）/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>紫色</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>艾莉薇（韩版）/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>蓝色</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>艾莉薇（韩版）/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>粉色</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>艾莉薇（韩版）/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>白色</t>
+    </r>
+  </si>
+  <si>
+    <t>奥地利公主VOLUME</t>
+  </si>
+  <si>
+    <r>
+      <t>乔雅登（欧版）/5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>号</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">乔雅登（欧版）/6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>号</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>乔雅登（欧版）/7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>号</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>乔雅登（欧版）/8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>号</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>乔雅登/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>丰颜</t>
+    </r>
+  </si>
   <si>
     <t>品牌/型号</t>
   </si>
   <si>
-    <t>规格</t>
-  </si>
-  <si>
-    <t>昨日价格</t>
-  </si>
-  <si>
-    <t>今日价格</t>
-  </si>
-  <si>
-    <t>乔雅登（韩版）/5号 丰颜</t>
+    <t>芮得怡（瑞德喜）/面部填充剂（欧版浅蓝）</t>
+  </si>
+  <si>
+    <t>1.5ml/支/盒</t>
+  </si>
+  <si>
+    <t>芮得怡（瑞德喜）/面部填充剂（欧版深蓝）</t>
+  </si>
+  <si>
+    <t>（含麻）1.5ml/支/盒</t>
+  </si>
+  <si>
+    <t>芮得怡（瑞德喜）/面部填充剂（韩版浅蓝）</t>
+  </si>
+  <si>
+    <t>乔雅登SKINVIVE长效水光韩版</t>
   </si>
   <si>
     <t>1ml*2支/盒</t>
   </si>
   <si>
-    <t>乔雅登（韩版）/6号 朔颜</t>
-  </si>
-  <si>
-    <t>乔雅登（韩版）/7号 缇颜</t>
-  </si>
-  <si>
-    <t>乔雅登（韩版）/8号 质颜</t>
-  </si>
-  <si>
-    <t>瑞蓝（欧版）/2号</t>
+    <t>塑然雅/塑颜萃塑妍萃 Sculptra（欧版）</t>
+  </si>
+  <si>
+    <t>2 瓶 / 盒 × 367.5mg / 瓶</t>
+  </si>
+  <si>
+    <t>爱塑美/臻爱塑菲（韩版）/童颜</t>
+  </si>
+  <si>
+    <t>200mg/瓶/盒</t>
+  </si>
+  <si>
+    <t>韩版肤丽美</t>
   </si>
   <si>
     <t>1ml/支/盒</t>
-  </si>
-  <si>
-    <t>¥580</t>
-  </si>
-  <si>
-    <t>瑞蓝（欧版）/3号</t>
-  </si>
-  <si>
-    <t>¥620</t>
-  </si>
-  <si>
-    <t>瑞蓝（欧版）/4号</t>
-  </si>
-  <si>
-    <t>¥640</t>
-  </si>
-  <si>
-    <t>瑞蓝（欧版）/5号</t>
-  </si>
-  <si>
-    <t>瑞蓝（欧版）/6号</t>
-  </si>
-  <si>
-    <t>瑞蓝（欧版）/refyne</t>
-  </si>
-  <si>
-    <t>瑞蓝（欧版）/Kysse唇部</t>
-  </si>
-  <si>
-    <t>姣兰 / 经典玻尿酸</t>
-  </si>
-  <si>
-    <t>姣兰 / Lips 唇部玻尿酸</t>
-  </si>
-  <si>
-    <t>艾莉薇（韩版）/紫色</t>
-  </si>
-  <si>
-    <t>艾莉薇（韩版）/蓝色</t>
-  </si>
-  <si>
-    <t>艾莉薇（韩版）/粉色</t>
-  </si>
-  <si>
-    <t>艾莉薇（韩版）/白色</t>
-  </si>
-  <si>
-    <t>奥地利公主VOLUME</t>
-  </si>
-  <si>
-    <t>芮得怡（瑞德喜）/面部填充剂（欧版浅蓝）</t>
-  </si>
-  <si>
-    <t>1.5ml/支/盒</t>
-  </si>
-  <si>
-    <t>芮得怡（瑞德喜）/面部填充剂（欧版深蓝）</t>
-  </si>
-  <si>
-    <t>（含麻）1.5ml/支/盒</t>
-  </si>
-  <si>
-    <t>芮得怡（瑞德喜）/面部填充剂（韩版浅蓝）</t>
-  </si>
-  <si>
-    <t>乔雅登SKINVIVE长效水光韩版</t>
-  </si>
-  <si>
-    <t>塑然雅/塑颜萃塑妍萃 Sculptra（欧版）</t>
-  </si>
-  <si>
-    <t>2 瓶 / 盒 × 367.5mg / 瓶</t>
-  </si>
-  <si>
-    <t>爱塑美/臻爱塑菲（韩版）/童颜</t>
-  </si>
-  <si>
-    <t>200mg/瓶/盒</t>
-  </si>
-  <si>
-    <t>韩版肤丽美</t>
   </si>
   <si>
     <t>双美/肤莱美</t>
@@ -270,15 +654,15 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
   <numFmts count="5">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="6" formatCode="&quot;￥&quot;#,##0;[Red]&quot;￥&quot;\-#,##0"/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -312,7 +696,56 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF27AE60"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -326,16 +759,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -343,22 +768,6 @@
     <font>
       <b/>
       <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -375,30 +784,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -413,9 +799,32 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -427,8 +836,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -442,24 +852,36 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="35">
@@ -483,13 +905,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -507,13 +983,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -531,19 +1007,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -555,13 +1037,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -579,19 +1067,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -604,66 +1086,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -693,6 +1115,30 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -712,30 +1158,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -772,15 +1194,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -789,155 +1202,164 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -954,70 +1376,215 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="6" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
+    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
+    <cellStyle name="输入" xfId="4" builtinId="20"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
+    <cellStyle name="货币" xfId="7" builtinId="4"/>
+    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
+    <cellStyle name="百分比" xfId="9" builtinId="5"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
+    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
+    <cellStyle name="计算" xfId="15" builtinId="22"/>
+    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
+    <cellStyle name="适中" xfId="17" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
+    <cellStyle name="好" xfId="19" builtinId="26"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
     <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="差" xfId="22" builtinId="27"/>
+    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
+    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
+    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
+    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
+    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
+    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
+    <cellStyle name="标题" xfId="33" builtinId="15"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
+    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
     <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="注释" xfId="37" builtinId="10"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
+    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
+    <cellStyle name="超链接" xfId="41" builtinId="8"/>
+    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
+    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
+    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <dxfs count="10">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="267968C86FFD4C36ACC19EA1FD1885CA">
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+    </tableStyle>
+  </tableStyles>
 </styleSheet>
 </file>
 
@@ -1300,14 +1867,15 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D444"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -1322,8 +1890,8 @@
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="3"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="3"/>
@@ -1923,7 +2491,7 @@
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
-      <c r="D102" s="7"/>
+      <c r="D102" s="13"/>
     </row>
     <row r="103" ht="22.05" customHeight="1" spans="1:4">
       <c r="A103" s="3"/>
@@ -3984,19 +4552,19 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="7" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="21.5555555555556" customWidth="1"/>
+    <col min="2" max="2" width="21.5535714285714" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4010,10 +4578,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C2" s="2">
         <v>470</v>
@@ -4024,10 +4592,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C3" s="2">
         <v>180</v>
@@ -4038,10 +4606,10 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C4" s="2">
         <v>840</v>
@@ -4052,10 +4620,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C5" s="2">
         <v>3000</v>
@@ -4066,10 +4634,10 @@
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C6" s="2">
         <v>380</v>
@@ -4080,10 +4648,10 @@
     </row>
     <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C7" s="2">
         <v>290</v>
@@ -4094,10 +4662,10 @@
     </row>
     <row r="8" ht="22.05" customHeight="1" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C8" s="2">
         <v>330</v>
@@ -4113,10 +4681,10 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -4124,7 +4692,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4143,10 +4711,10 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -4154,7 +4722,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4173,10 +4741,10 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -4184,7 +4752,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4203,335 +4771,405 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="20.1111111111111" customWidth="1"/>
+    <col min="1" max="1" width="20.1071428571429" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" ht="15.4" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
-  <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="29.7777777777778" customWidth="1"/>
-    <col min="2" max="2" width="15.2222222222222" customWidth="1"/>
-    <col min="3" max="4" width="14" customWidth="1"/>
+    <col min="1" max="1" width="26.8214285714286" customWidth="1"/>
+    <col min="2" max="2" width="13.5803571428571" customWidth="1"/>
+    <col min="3" max="4" width="12.8660714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.05" customHeight="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A2" s="2" t="s">
+    <row r="2" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="8">
         <v>1550</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="8">
         <v>1550</v>
       </c>
     </row>
-    <row r="3" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A3" s="3" t="s">
+    <row r="3" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="8">
         <v>1650</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="8">
         <v>1650</v>
       </c>
     </row>
-    <row r="4" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A4" s="3" t="s">
+    <row r="4" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="8">
         <v>1650</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="8">
         <v>1650</v>
       </c>
     </row>
-    <row r="5" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A5" s="3" t="s">
+    <row r="5" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="8">
         <v>1540</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="8">
         <v>1540</v>
       </c>
     </row>
-    <row r="6" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A6" s="2" t="s">
+    <row r="6" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A6" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A7" s="3" t="s">
+    <row r="7" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A7" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A8" s="2" t="s">
+    <row r="8" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A8" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A9" s="3" t="s">
+    <row r="9" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A9" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A10" s="3" t="s">
+    <row r="10" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A10" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A11" s="2" t="s">
+    <row r="11" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A11" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A12" s="2" t="s">
+    <row r="12" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A12" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A13" s="2" t="s">
+    <row r="13" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A13" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="7">
         <v>250</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="7">
         <v>250</v>
       </c>
     </row>
-    <row r="14" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A14" s="3" t="s">
+    <row r="14" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A14" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="9">
         <v>260</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="9">
         <v>260</v>
       </c>
     </row>
-    <row r="15" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A15" s="2" t="s">
+    <row r="15" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A15" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="9">
         <v>160</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="9">
         <v>160</v>
       </c>
     </row>
-    <row r="16" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A16" s="3" t="s">
+    <row r="16" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A16" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="9">
         <v>160</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="9">
         <v>160</v>
       </c>
     </row>
-    <row r="17" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A17" s="2" t="s">
+    <row r="17" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A17" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="9">
         <v>160</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="9">
         <v>160</v>
       </c>
     </row>
-    <row r="18" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A18" s="3" t="s">
+    <row r="18" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A18" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="9">
         <v>160</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="9">
         <v>160</v>
       </c>
     </row>
-    <row r="19" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A19" s="3" t="s">
+    <row r="19" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A19" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="9">
         <v>600</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="9">
         <v>600</v>
+      </c>
+    </row>
+    <row r="20" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A20" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="11">
+        <v>1900</v>
+      </c>
+      <c r="D20" s="11">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="21" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A21" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="11">
+        <v>2090</v>
+      </c>
+      <c r="D21" s="11">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="22" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A22" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="11">
+        <v>2090</v>
+      </c>
+      <c r="D22" s="11">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="23" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A23" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="11">
+        <v>2090</v>
+      </c>
+      <c r="D23" s="11">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="24" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A24" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="11">
+        <v>5350</v>
+      </c>
+      <c r="D24" s="11">
+        <v>5350</v>
       </c>
     </row>
   </sheetData>
@@ -4541,19 +5179,19 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="3" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="44.5555555555556" customWidth="1"/>
-    <col min="2" max="2" width="34.7777777777778" customWidth="1"/>
+    <col min="1" max="1" width="44.5535714285714" customWidth="1"/>
+    <col min="2" max="2" width="34.7767857142857" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4567,10 +5205,10 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C2" s="3">
         <v>1360</v>
@@ -4581,10 +5219,10 @@
     </row>
     <row r="3" ht="21" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C3" s="3">
         <v>1390</v>
@@ -4595,10 +5233,10 @@
     </row>
     <row r="4" ht="21" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C4" s="3">
         <v>1340</v>
@@ -4614,10 +5252,10 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D167"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -4625,7 +5263,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4639,10 +5277,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="C2" s="3">
         <v>870</v>
@@ -5648,10 +6286,10 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -5659,7 +6297,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -5678,19 +6316,19 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="2" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="36.7777777777778" customWidth="1"/>
-    <col min="2" max="2" width="25.7777777777778" customWidth="1"/>
+    <col min="1" max="1" width="36.7767857142857" customWidth="1"/>
+    <col min="2" max="2" width="25.7767857142857" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -5704,10 +6342,10 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C2" s="3">
         <v>2300</v>
@@ -5718,10 +6356,10 @@
     </row>
     <row r="3" ht="21" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C3" s="3">
         <v>1860</v>
@@ -5737,10 +6375,10 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -5748,7 +6386,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -5762,10 +6400,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3">
         <v>350</v>
@@ -5776,10 +6414,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C3" s="2">
         <v>3430</v>
@@ -5790,10 +6428,10 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C4" s="3">
         <v>1000</v>
@@ -5804,10 +6442,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C5" s="2">
         <v>1120</v>
@@ -5818,10 +6456,10 @@
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C6" s="2">
         <v>1730</v>
@@ -5832,10 +6470,10 @@
     </row>
     <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="C7" s="2">
         <v>1590</v>
@@ -5846,10 +6484,10 @@
     </row>
     <row r="8" ht="22.05" customHeight="1" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C8" s="2">
         <v>1350</v>
@@ -5860,10 +6498,10 @@
     </row>
     <row r="9" ht="22.05" customHeight="1" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C9" s="2">
         <v>620</v>
@@ -5874,10 +6512,10 @@
     </row>
     <row r="10" ht="22.05" customHeight="1" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C10" s="2">
         <v>735</v>
@@ -5888,10 +6526,10 @@
     </row>
     <row r="11" ht="22.05" customHeight="1" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C11" s="2">
         <v>780</v>
@@ -5907,10 +6545,10 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -5918,7 +6556,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -5937,10 +6575,10 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="2" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -5948,7 +6586,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -5960,12 +6598,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" ht="15.4" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="C2" s="4">
         <v>3350</v>
@@ -5974,12 +6612,12 @@
         <v>3350</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" ht="15.4" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="C3" s="4">
         <v>3200</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19115" windowHeight="10860" firstSheet="4"/>
+    <workbookView windowWidth="19115" windowHeight="10860" firstSheet="4" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -27,9 +27,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84">
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>品牌/</t>
     </r>
     <r>
@@ -54,6 +61,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>乔雅登（韩版）/5</t>
     </r>
     <r>
@@ -86,6 +99,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>1ml*2</t>
     </r>
     <r>
@@ -118,6 +137,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>乔雅登（韩版）/6</t>
     </r>
     <r>
@@ -150,6 +175,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>乔雅登（韩版）/7</t>
     </r>
     <r>
@@ -182,6 +213,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>乔雅登（韩版）/8</t>
     </r>
     <r>
@@ -214,6 +251,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>瑞蓝（欧版）/2</t>
     </r>
     <r>
@@ -228,6 +271,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>1ml/</t>
     </r>
     <r>
@@ -263,6 +312,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>瑞蓝（欧版）/3</t>
     </r>
     <r>
@@ -280,6 +335,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>瑞蓝（欧版）/4</t>
     </r>
     <r>
@@ -297,6 +358,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>瑞蓝（欧版）/5</t>
     </r>
     <r>
@@ -311,6 +378,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>瑞蓝（欧版）/6</t>
     </r>
     <r>
@@ -328,6 +401,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>瑞蓝（欧版）/Kysse</t>
     </r>
     <r>
@@ -342,6 +421,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">姣兰 / </t>
     </r>
     <r>
@@ -356,6 +441,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">姣兰 / Lips </t>
     </r>
     <r>
@@ -370,6 +461,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>艾莉薇（韩版）/</t>
     </r>
     <r>
@@ -384,6 +481,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>艾莉薇（韩版）/</t>
     </r>
     <r>
@@ -398,6 +501,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>艾莉薇（韩版）/</t>
     </r>
     <r>
@@ -412,6 +521,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>艾莉薇（韩版）/</t>
     </r>
     <r>
@@ -429,6 +544,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>乔雅登（欧版）/5</t>
     </r>
     <r>
@@ -442,7 +563,17 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">1ml*2支/盒
+</t>
+  </si>
+  <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">乔雅登（欧版）/6 </t>
     </r>
     <r>
@@ -457,6 +588,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>乔雅登（欧版）/7</t>
     </r>
     <r>
@@ -471,6 +608,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>乔雅登（欧版）/8</t>
     </r>
     <r>
@@ -485,6 +628,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>乔雅登/</t>
     </r>
     <r>
@@ -656,11 +805,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
   <numFmts count="5">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="6" formatCode="&quot;￥&quot;#,##0;[Red]&quot;￥&quot;\-#,##0"/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="30">
     <font>
@@ -722,38 +871,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -767,7 +892,7 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -790,6 +915,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -799,7 +931,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -813,8 +968,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -830,36 +993,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -911,19 +1060,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -935,7 +1102,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -947,37 +1222,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -989,103 +1234,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1114,17 +1263,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1134,21 +1277,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1173,6 +1301,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1203,96 +1346,102 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1301,65 +1450,65 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1386,9 +1535,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1890,8 +2036,8 @@
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="3"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="3"/>
@@ -2491,7 +2637,7 @@
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
-      <c r="D102" s="13"/>
+      <c r="D102" s="12"/>
     </row>
     <row r="103" ht="22.05" customHeight="1" spans="1:4">
       <c r="A103" s="3"/>
@@ -4564,7 +4710,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4578,10 +4724,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C2" s="2">
         <v>470</v>
@@ -4592,10 +4738,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C3" s="2">
         <v>180</v>
@@ -4606,10 +4752,10 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C4" s="2">
         <v>840</v>
@@ -4620,10 +4766,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C5" s="2">
         <v>3000</v>
@@ -4634,10 +4780,10 @@
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C6" s="2">
         <v>380</v>
@@ -4648,10 +4794,10 @@
     </row>
     <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C7" s="2">
         <v>290</v>
@@ -4662,10 +4808,10 @@
     </row>
     <row r="8" ht="22.05" customHeight="1" spans="1:4">
       <c r="A8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="C8" s="2">
         <v>330</v>
@@ -4692,7 +4838,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4722,7 +4868,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4752,7 +4898,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4781,42 +4927,42 @@
   <sheetData>
     <row r="1" ht="15.4" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -5107,68 +5253,68 @@
         <v>27</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="11">
-        <v>1900</v>
-      </c>
-      <c r="D20" s="11">
-        <v>1900</v>
+        <v>28</v>
+      </c>
+      <c r="C20" s="10">
+        <v>1800</v>
+      </c>
+      <c r="D20" s="10">
+        <v>1800</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1" spans="1:4">
       <c r="A21" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="11">
-        <v>2090</v>
-      </c>
-      <c r="D21" s="11">
-        <v>2090</v>
+      <c r="C21" s="10">
+        <v>1900</v>
+      </c>
+      <c r="D21" s="10">
+        <v>1900</v>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1" spans="1:4">
       <c r="A22" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="11">
-        <v>2090</v>
-      </c>
-      <c r="D22" s="11">
-        <v>2090</v>
+        <v>28</v>
+      </c>
+      <c r="C22" s="10">
+        <v>1960</v>
+      </c>
+      <c r="D22" s="10">
+        <v>1960</v>
       </c>
     </row>
     <row r="23" ht="22.5" customHeight="1" spans="1:4">
       <c r="A23" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="11">
-        <v>2090</v>
-      </c>
-      <c r="D23" s="11">
-        <v>2090</v>
+        <v>28</v>
+      </c>
+      <c r="C23" s="10">
+        <v>1960</v>
+      </c>
+      <c r="D23" s="10">
+        <v>1960</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1" spans="1:4">
       <c r="A24" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="11">
+        <v>28</v>
+      </c>
+      <c r="C24" s="10">
         <v>5350</v>
       </c>
-      <c r="D24" s="11">
+      <c r="D24" s="10">
         <v>5350</v>
       </c>
     </row>
@@ -5191,7 +5337,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -5205,10 +5351,10 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" s="3">
         <v>1360</v>
@@ -5219,10 +5365,10 @@
     </row>
     <row r="3" ht="21" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C3" s="3">
         <v>1390</v>
@@ -5233,10 +5379,10 @@
     </row>
     <row r="4" ht="21" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3">
         <v>1340</v>
@@ -5263,7 +5409,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -5277,10 +5423,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C2" s="3">
         <v>870</v>
@@ -6297,7 +6443,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -6328,7 +6474,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -6342,10 +6488,10 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C2" s="3">
         <v>2300</v>
@@ -6356,10 +6502,10 @@
     </row>
     <row r="3" ht="21" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C3" s="3">
         <v>1860</v>
@@ -6386,7 +6532,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -6400,10 +6546,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C2" s="3">
         <v>350</v>
@@ -6414,10 +6560,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C3" s="2">
         <v>3430</v>
@@ -6428,10 +6574,10 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C4" s="3">
         <v>1000</v>
@@ -6442,10 +6588,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="C5" s="2">
         <v>1120</v>
@@ -6456,10 +6602,10 @@
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C6" s="2">
         <v>1730</v>
@@ -6470,10 +6616,10 @@
     </row>
     <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C7" s="2">
         <v>1590</v>
@@ -6484,10 +6630,10 @@
     </row>
     <row r="8" ht="22.05" customHeight="1" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C8" s="2">
         <v>1350</v>
@@ -6498,10 +6644,10 @@
     </row>
     <row r="9" ht="22.05" customHeight="1" spans="1:4">
       <c r="A9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="C9" s="2">
         <v>620</v>
@@ -6512,10 +6658,10 @@
     </row>
     <row r="10" ht="22.05" customHeight="1" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C10" s="2">
         <v>735</v>
@@ -6526,10 +6672,10 @@
     </row>
     <row r="11" ht="22.05" customHeight="1" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11" s="2">
         <v>780</v>
@@ -6556,7 +6702,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -6586,7 +6732,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -6600,10 +6746,10 @@
     </row>
     <row r="2" ht="15.4" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C2" s="4">
         <v>3350</v>
@@ -6614,10 +6760,10 @@
     </row>
     <row r="3" ht="15.4" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C3" s="4">
         <v>3200</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -567,24 +567,7 @@
 </t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">乔雅登（欧版）/6 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>号</t>
-    </r>
+    <t>乔雅登（欧版）/6号</t>
   </si>
   <si>
     <r>
@@ -806,10 +789,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
   <numFmts count="5">
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="6" formatCode="&quot;￥&quot;#,##0;[Red]&quot;￥&quot;\-#,##0"/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="30">
     <font>
@@ -884,6 +867,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
@@ -892,7 +898,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -907,9 +913,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -922,14 +951,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
@@ -937,9 +958,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -953,24 +982,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -978,37 +992,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1060,13 +1043,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1084,37 +1109,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1126,115 +1217,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1272,11 +1255,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1306,31 +1319,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1345,103 +1343,88 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1450,55 +1433,55 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19115" windowHeight="10860" firstSheet="4" activeTab="1"/>
+    <workbookView windowWidth="17604" windowHeight="10428" firstSheet="6" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -22,12 +22,25 @@
     <sheet name="医用敷贴" sheetId="14" r:id="rId13"/>
     <sheet name="删除" sheetId="15" r:id="rId14"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="88">
   <si>
     <r>
       <rPr>
@@ -543,6 +556,15 @@
     <t>奥地利公主VOLUME</t>
   </si>
   <si>
+    <t>乔雅登（欧版）/2号</t>
+  </si>
+  <si>
+    <t>乔雅登（欧版）/3号</t>
+  </si>
+  <si>
+    <t>乔雅登（欧版）/4号</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -654,6 +676,9 @@
     <t>1ml*2支/盒</t>
   </si>
   <si>
+    <t>乔雅登SKINVIVE长效水光欧版</t>
+  </si>
+  <si>
     <t>塑然雅/塑颜萃塑妍萃 Sculptra（欧版）</t>
   </si>
   <si>
@@ -786,13 +811,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="5">
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="6" formatCode="&quot;￥&quot;#,##0;[Red]&quot;￥&quot;\-#,##0"/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="6" formatCode="&quot;￥&quot;#,##0;[Red]&quot;￥&quot;\-#,##0"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="30">
     <font>
@@ -839,12 +864,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Microsoft YaHei"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF27AE60"/>
@@ -853,45 +872,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -913,9 +927,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -929,13 +950,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
@@ -944,41 +958,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -997,11 +988,32 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1012,6 +1024,19 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1037,7 +1062,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1049,13 +1086,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1067,25 +1104,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1097,13 +1176,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1121,67 +1212,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1193,31 +1224,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1246,39 +1271,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -1303,17 +1295,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1333,6 +1319,45 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -1346,152 +1371,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1520,66 +1545,63 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="6" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
-    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
-    <cellStyle name="输入" xfId="4" builtinId="20"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
-    <cellStyle name="货币" xfId="7" builtinId="4"/>
-    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
-    <cellStyle name="百分比" xfId="9" builtinId="5"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
-    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
-    <cellStyle name="计算" xfId="15" builtinId="22"/>
-    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
-    <cellStyle name="适中" xfId="17" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
-    <cellStyle name="好" xfId="19" builtinId="26"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
     <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="差" xfId="22" builtinId="27"/>
-    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
-    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
-    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
-    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
-    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
-    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
-    <cellStyle name="标题" xfId="33" builtinId="15"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
-    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
     <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="注释" xfId="37" builtinId="10"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
-    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
-    <cellStyle name="超链接" xfId="41" builtinId="8"/>
-    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
-    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
-    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="10">
     <dxf>
@@ -1701,7 +1723,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="267968C86FFD4C36ACC19EA1FD1885CA">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
       <tableStyleElement type="headerRow" dxfId="9"/>
       <tableStyleElement type="totalRow" dxfId="8"/>
       <tableStyleElement type="firstRowStripe" dxfId="7"/>
@@ -1714,6 +1736,11 @@
       <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1996,15 +2023,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D444"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -2019,8 +2045,8 @@
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="3"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="3"/>
@@ -2620,7 +2646,7 @@
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
-      <c r="D102" s="12"/>
+      <c r="D102" s="11"/>
     </row>
     <row r="103" ht="22.05" customHeight="1" spans="1:4">
       <c r="A103" s="3"/>
@@ -4681,19 +4707,19 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="7" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="21.5535714285714" customWidth="1"/>
+    <col min="2" max="2" width="21.5555555555556" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4707,10 +4733,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C2" s="2">
         <v>470</v>
@@ -4721,10 +4747,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C3" s="2">
         <v>180</v>
@@ -4735,10 +4761,10 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C4" s="2">
         <v>840</v>
@@ -4749,10 +4775,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C5" s="2">
         <v>3000</v>
@@ -4763,10 +4789,10 @@
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C6" s="2">
         <v>380</v>
@@ -4777,10 +4803,10 @@
     </row>
     <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C7" s="2">
         <v>290</v>
@@ -4791,10 +4817,10 @@
     </row>
     <row r="8" ht="22.05" customHeight="1" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C8" s="2">
         <v>330</v>
@@ -4810,10 +4836,10 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -4821,7 +4847,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4840,10 +4866,10 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -4851,7 +4877,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4870,10 +4896,10 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -4881,7 +4907,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4900,52 +4926,52 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="7"/>
+  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="20.1071428571429" customWidth="1"/>
+    <col min="1" max="1" width="20.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.4" spans="1:1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -4955,14 +4981,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="26.8214285714286" customWidth="1"/>
-    <col min="2" max="2" width="13.5803571428571" customWidth="1"/>
-    <col min="3" max="4" width="12.8660714285714" customWidth="1"/>
+    <col min="1" max="1" width="26.8240740740741" customWidth="1"/>
+    <col min="2" max="2" width="13.5833333333333" customWidth="1"/>
+    <col min="3" max="4" width="12.8703703703704" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1" spans="1:4">
@@ -5218,7 +5244,7 @@
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1" spans="1:4">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="7" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="9" t="s">
@@ -5232,72 +5258,114 @@
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1" spans="1:4">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="9" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="9">
+        <v>975</v>
+      </c>
+      <c r="D20" s="9">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="21" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A21" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="10">
+      <c r="B21" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="9">
+        <v>1440</v>
+      </c>
+      <c r="D21" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="22" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A22" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="9">
+        <v>1440</v>
+      </c>
+      <c r="D22" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="23" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A23" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="9">
         <v>1800</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D23" s="9">
         <v>1800</v>
       </c>
     </row>
-    <row r="21" ht="22.5" customHeight="1" spans="1:4">
-      <c r="A21" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="10">
+    <row r="24" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A24" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="9">
         <v>1900</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D24" s="9">
         <v>1900</v>
       </c>
     </row>
-    <row r="22" ht="22.5" customHeight="1" spans="1:4">
-      <c r="A22" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="10">
+    <row r="25" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A25" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" s="9">
         <v>1960</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D25" s="9">
         <v>1960</v>
       </c>
     </row>
-    <row r="23" ht="22.5" customHeight="1" spans="1:4">
-      <c r="A23" s="10" t="s">
+    <row r="26" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A26" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" s="10">
+      <c r="C26" s="9">
         <v>1960</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D26" s="9">
         <v>1960</v>
       </c>
     </row>
-    <row r="24" ht="22.5" customHeight="1" spans="1:4">
-      <c r="A24" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" s="10">
+    <row r="27" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A27" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="9">
         <v>5350</v>
       </c>
-      <c r="D24" s="10">
+      <c r="D27" s="9">
         <v>5350</v>
       </c>
     </row>
@@ -5308,19 +5376,19 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="3" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="44.5535714285714" customWidth="1"/>
-    <col min="2" max="2" width="34.7767857142857" customWidth="1"/>
+    <col min="1" max="1" width="44.5555555555556" customWidth="1"/>
+    <col min="2" max="2" width="34.7777777777778" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -5334,10 +5402,10 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C2" s="3">
         <v>1360</v>
@@ -5348,10 +5416,10 @@
     </row>
     <row r="3" ht="21" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C3" s="3">
         <v>1390</v>
@@ -5362,10 +5430,10 @@
     </row>
     <row r="4" ht="21" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="C4" s="3">
         <v>1340</v>
@@ -5381,10 +5449,10 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D167"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -5392,7 +5460,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -5406,10 +5474,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C2" s="3">
         <v>870</v>
@@ -5419,10 +5487,18 @@
       </c>
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
+      <c r="A3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="2">
+        <v>600</v>
+      </c>
+      <c r="D3" s="2">
+        <v>600</v>
+      </c>
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="3"/>
@@ -6415,10 +6491,10 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -6426,7 +6502,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -6445,19 +6521,19 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="2" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="36.7767857142857" customWidth="1"/>
-    <col min="2" max="2" width="25.7767857142857" customWidth="1"/>
+    <col min="1" max="1" width="36.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="25.7777777777778" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -6471,10 +6547,10 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2" s="3">
         <v>2300</v>
@@ -6485,10 +6561,10 @@
     </row>
     <row r="3" ht="21" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C3" s="3">
         <v>1860</v>
@@ -6504,10 +6580,10 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -6515,7 +6591,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -6529,10 +6605,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C2" s="3">
         <v>350</v>
@@ -6543,10 +6619,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C3" s="2">
         <v>3430</v>
@@ -6557,10 +6633,10 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C4" s="3">
         <v>1000</v>
@@ -6571,10 +6647,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C5" s="2">
         <v>1120</v>
@@ -6585,10 +6661,10 @@
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C6" s="2">
         <v>1730</v>
@@ -6599,10 +6675,10 @@
     </row>
     <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C7" s="2">
         <v>1590</v>
@@ -6613,10 +6689,10 @@
     </row>
     <row r="8" ht="22.05" customHeight="1" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C8" s="2">
         <v>1350</v>
@@ -6627,10 +6703,10 @@
     </row>
     <row r="9" ht="22.05" customHeight="1" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C9" s="2">
         <v>620</v>
@@ -6641,10 +6717,10 @@
     </row>
     <row r="10" ht="22.05" customHeight="1" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C10" s="2">
         <v>735</v>
@@ -6655,10 +6731,10 @@
     </row>
     <row r="11" ht="22.05" customHeight="1" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C11" s="2">
         <v>780</v>
@@ -6674,10 +6750,10 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -6685,7 +6761,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -6704,10 +6780,10 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="2" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -6715,7 +6791,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -6727,12 +6803,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="15.4" spans="1:4">
+    <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C2" s="4">
         <v>3350</v>
@@ -6741,12 +6817,12 @@
         <v>3350</v>
       </c>
     </row>
-    <row r="3" ht="15.4" spans="1:4">
+    <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C3" s="4">
         <v>3200</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17604" windowHeight="10428" firstSheet="6" activeTab="13"/>
+    <workbookView windowWidth="17604" windowHeight="10428" firstSheet="6" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -22,25 +22,12 @@
     <sheet name="医用敷贴" sheetId="14" r:id="rId13"/>
     <sheet name="删除" sheetId="15" r:id="rId14"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89">
   <si>
     <r>
       <rPr>
@@ -559,7 +546,14 @@
     <t>乔雅登（欧版）/2号</t>
   </si>
   <si>
+    <t>0.55ml*2支/盒</t>
+  </si>
+  <si>
     <t>乔雅登（欧版）/3号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1ml*2支/盒
+</t>
   </si>
   <si>
     <t>乔雅登（欧版）/4号</t>
@@ -585,10 +579,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">1ml*2支/盒
-</t>
-  </si>
-  <si>
     <t>乔雅登（欧版）/6号</t>
   </si>
   <si>
@@ -811,15 +801,15 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
   <numFmts count="5">
     <numFmt numFmtId="6" formatCode="&quot;￥&quot;#,##0;[Red]&quot;￥&quot;\-#,##0"/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -865,8 +855,59 @@
     </font>
     <font>
       <b/>
+      <sz val="10.5"/>
+      <color rgb="FF1A1020"/>
+      <name val="-apple-system"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="8.25"/>
+      <color rgb="FF9A8A8E"/>
+      <name val="-apple-system"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF27AE60"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -880,16 +921,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -900,6 +933,14 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -920,23 +961,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -944,7 +970,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -958,24 +992,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -989,13 +1007,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -1003,17 +1014,24 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1030,13 +1048,6 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1062,13 +1073,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1086,84 +1127,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1176,31 +1139,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1212,7 +1175,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1230,19 +1217,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1271,26 +1282,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1304,17 +1300,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1351,15 +1341,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -1368,155 +1349,185 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1545,63 +1556,66 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="6" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
+    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
+    <cellStyle name="输入" xfId="4" builtinId="20"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
+    <cellStyle name="货币" xfId="7" builtinId="4"/>
+    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
+    <cellStyle name="百分比" xfId="9" builtinId="5"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
+    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
+    <cellStyle name="计算" xfId="15" builtinId="22"/>
+    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
+    <cellStyle name="适中" xfId="17" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
+    <cellStyle name="好" xfId="19" builtinId="26"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
     <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="差" xfId="22" builtinId="27"/>
+    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
+    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
+    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
+    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
+    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
+    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
+    <cellStyle name="标题" xfId="33" builtinId="15"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
+    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
     <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="注释" xfId="37" builtinId="10"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
+    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
+    <cellStyle name="超链接" xfId="41" builtinId="8"/>
+    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
+    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
+    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
   </cellStyles>
   <dxfs count="10">
     <dxf>
@@ -1723,7 +1737,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="267968C86FFD4C36ACC19EA1FD1885CA">
       <tableStyleElement type="headerRow" dxfId="9"/>
       <tableStyleElement type="totalRow" dxfId="8"/>
       <tableStyleElement type="firstRowStripe" dxfId="7"/>
@@ -1736,11 +1750,6 @@
       <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -2023,14 +2032,15 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D444"/>
-  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -2045,8 +2055,8 @@
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="3"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="3"/>
@@ -2646,7 +2656,7 @@
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
-      <c r="D102" s="11"/>
+      <c r="D102" s="14"/>
     </row>
     <row r="103" ht="22.05" customHeight="1" spans="1:4">
       <c r="A103" s="3"/>
@@ -4707,19 +4717,19 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="7" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="21.5555555555556" customWidth="1"/>
+    <col min="2" max="2" width="21.5535714285714" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4733,10 +4743,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C2" s="2">
         <v>470</v>
@@ -4747,10 +4757,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2">
         <v>180</v>
@@ -4761,10 +4771,10 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C4" s="2">
         <v>840</v>
@@ -4775,10 +4785,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C5" s="2">
         <v>3000</v>
@@ -4789,10 +4799,10 @@
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C6" s="2">
         <v>380</v>
@@ -4803,10 +4813,10 @@
     </row>
     <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C7" s="2">
         <v>290</v>
@@ -4817,10 +4827,10 @@
     </row>
     <row r="8" ht="22.05" customHeight="1" spans="1:4">
       <c r="A8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="C8" s="2">
         <v>330</v>
@@ -4836,10 +4846,10 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -4847,7 +4857,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4866,10 +4876,10 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -4877,7 +4887,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4896,10 +4906,10 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -4907,7 +4917,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4926,52 +4936,52 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelRow="7"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="20.1111111111111" customWidth="1"/>
+    <col min="1" max="1" width="20.1071428571429" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" ht="15.4" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -4981,14 +4991,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D27"/>
-  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="26.8240740740741" customWidth="1"/>
-    <col min="2" max="2" width="13.5833333333333" customWidth="1"/>
-    <col min="3" max="4" width="12.8703703703704" customWidth="1"/>
+    <col min="1" max="1" width="26.8214285714286" customWidth="1"/>
+    <col min="2" max="2" width="13.5803571428571" customWidth="1"/>
+    <col min="3" max="4" width="12.8660714285714" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1" spans="1:4">
@@ -5258,11 +5268,11 @@
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1" spans="1:4">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>10</v>
+      <c r="B20" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="C20" s="9">
         <v>975</v>
@@ -5272,11 +5282,11 @@
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1" spans="1:4">
-      <c r="A21" s="7" t="s">
-        <v>28</v>
+      <c r="A21" s="12" t="s">
+        <v>29</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C21" s="9">
         <v>1440</v>
@@ -5286,11 +5296,11 @@
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1" spans="1:4">
-      <c r="A22" s="9" t="s">
-        <v>29</v>
+      <c r="A22" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C22" s="9">
         <v>1440</v>
@@ -5301,10 +5311,10 @@
     </row>
     <row r="23" ht="22.5" customHeight="1" spans="1:4">
       <c r="A23" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="9" t="s">
         <v>30</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>31</v>
       </c>
       <c r="C23" s="9">
         <v>1800</v>
@@ -5315,10 +5325,10 @@
     </row>
     <row r="24" ht="22.5" customHeight="1" spans="1:4">
       <c r="A24" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C24" s="9">
         <v>1900</v>
@@ -5329,10 +5339,10 @@
     </row>
     <row r="25" ht="22.5" customHeight="1" spans="1:4">
       <c r="A25" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C25" s="9">
         <v>1960</v>
@@ -5343,10 +5353,10 @@
     </row>
     <row r="26" ht="22.5" customHeight="1" spans="1:4">
       <c r="A26" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C26" s="9">
         <v>1960</v>
@@ -5357,10 +5367,10 @@
     </row>
     <row r="27" ht="22.5" customHeight="1" spans="1:4">
       <c r="A27" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C27" s="9">
         <v>5350</v>
@@ -5376,19 +5386,19 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="3" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="44.5555555555556" customWidth="1"/>
-    <col min="2" max="2" width="34.7777777777778" customWidth="1"/>
+    <col min="1" max="1" width="44.5535714285714" customWidth="1"/>
+    <col min="2" max="2" width="34.7767857142857" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -5402,10 +5412,10 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C2" s="3">
         <v>1360</v>
@@ -5416,10 +5426,10 @@
     </row>
     <row r="3" ht="21" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C3" s="3">
         <v>1390</v>
@@ -5430,10 +5440,10 @@
     </row>
     <row r="4" ht="21" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C4" s="3">
         <v>1340</v>
@@ -5449,10 +5459,10 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D167"/>
-  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -5460,7 +5470,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -5474,10 +5484,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3">
         <v>870</v>
@@ -5488,10 +5498,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="C3" s="2">
         <v>600</v>
@@ -6491,10 +6501,10 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -6502,7 +6512,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -6521,19 +6531,19 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="2" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="36.7777777777778" customWidth="1"/>
-    <col min="2" max="2" width="25.7777777777778" customWidth="1"/>
+    <col min="1" max="1" width="36.7767857142857" customWidth="1"/>
+    <col min="2" max="2" width="25.7767857142857" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -6547,10 +6557,10 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C2" s="3">
         <v>2300</v>
@@ -6561,10 +6571,10 @@
     </row>
     <row r="3" ht="21" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C3" s="3">
         <v>1860</v>
@@ -6580,10 +6590,10 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -6591,7 +6601,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -6605,10 +6615,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C2" s="3">
         <v>350</v>
@@ -6619,10 +6629,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C3" s="2">
         <v>3430</v>
@@ -6633,10 +6643,10 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C4" s="3">
         <v>1000</v>
@@ -6647,10 +6657,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="C5" s="2">
         <v>1120</v>
@@ -6661,10 +6671,10 @@
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6" s="2">
         <v>1730</v>
@@ -6675,10 +6685,10 @@
     </row>
     <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C7" s="2">
         <v>1590</v>
@@ -6689,10 +6699,10 @@
     </row>
     <row r="8" ht="22.05" customHeight="1" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C8" s="2">
         <v>1350</v>
@@ -6703,10 +6713,10 @@
     </row>
     <row r="9" ht="22.05" customHeight="1" spans="1:4">
       <c r="A9" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="C9" s="2">
         <v>620</v>
@@ -6717,10 +6727,10 @@
     </row>
     <row r="10" ht="22.05" customHeight="1" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C10" s="2">
         <v>735</v>
@@ -6731,10 +6741,10 @@
     </row>
     <row r="11" ht="22.05" customHeight="1" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C11" s="2">
         <v>780</v>
@@ -6750,10 +6760,10 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -6761,7 +6771,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -6780,10 +6790,10 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="2" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -6791,7 +6801,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -6803,12 +6813,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" ht="15.4" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C2" s="4">
         <v>3350</v>
@@ -6817,12 +6827,12 @@
         <v>3350</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" ht="15.4" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C3" s="4">
         <v>3200</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17604" windowHeight="10428" firstSheet="6" activeTab="1"/>
+    <workbookView windowWidth="18251" windowHeight="12120" firstSheet="6" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -22,12 +22,25 @@
     <sheet name="医用敷贴" sheetId="14" r:id="rId13"/>
     <sheet name="删除" sheetId="15" r:id="rId14"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="89">
   <si>
     <r>
       <rPr>
@@ -546,14 +559,7 @@
     <t>乔雅登（欧版）/2号</t>
   </si>
   <si>
-    <t>0.55ml*2支/盒</t>
-  </si>
-  <si>
     <t>乔雅登（欧版）/3号</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1ml*2支/盒
-</t>
   </si>
   <si>
     <t>乔雅登（欧版）/4号</t>
@@ -579,6 +585,10 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">1ml*2支/盒
+</t>
+  </si>
+  <si>
     <t>乔雅登（欧版）/6号</t>
   </si>
   <si>
@@ -720,7 +730,7 @@
     <t>悦白之几/17型</t>
   </si>
   <si>
-    <t>悦白之几/韵镜</t>
+    <t>悦白之几/韵境</t>
   </si>
   <si>
     <t>16mg/瓶/盒</t>
@@ -796,20 +806,23 @@
   </si>
   <si>
     <t>澳蕾诺/消消瓶</t>
+  </si>
+  <si>
+    <t>乔瑞嘉/帝美妮</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="5">
     <numFmt numFmtId="6" formatCode="&quot;￥&quot;#,##0;[Red]&quot;￥&quot;\-#,##0"/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -855,59 +868,8 @@
     </font>
     <font>
       <b/>
-      <sz val="10.5"/>
-      <color rgb="FF1A1020"/>
-      <name val="-apple-system"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="8.25"/>
-      <color rgb="FF9A8A8E"/>
-      <name val="-apple-system"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10.5"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF27AE60"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -921,8 +883,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -933,14 +903,6 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -961,8 +923,39 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -976,6 +969,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -984,9 +984,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1000,13 +999,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -1014,24 +1006,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1048,6 +1033,13 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1073,43 +1065,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1127,6 +1089,84 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1139,31 +1179,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1175,31 +1215,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1217,43 +1233,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1282,11 +1274,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1300,11 +1307,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1341,6 +1354,15 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -1349,185 +1371,155 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="32" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1556,66 +1548,63 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="6" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
-    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
-    <cellStyle name="输入" xfId="4" builtinId="20"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
-    <cellStyle name="货币" xfId="7" builtinId="4"/>
-    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
-    <cellStyle name="百分比" xfId="9" builtinId="5"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
-    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
-    <cellStyle name="计算" xfId="15" builtinId="22"/>
-    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
-    <cellStyle name="适中" xfId="17" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
-    <cellStyle name="好" xfId="19" builtinId="26"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
     <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="差" xfId="22" builtinId="27"/>
-    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
-    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
-    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
-    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
-    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
-    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
-    <cellStyle name="标题" xfId="33" builtinId="15"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
-    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
     <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="注释" xfId="37" builtinId="10"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
-    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
-    <cellStyle name="超链接" xfId="41" builtinId="8"/>
-    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
-    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
-    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="10">
     <dxf>
@@ -1737,7 +1726,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="267968C86FFD4C36ACC19EA1FD1885CA">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
       <tableStyleElement type="headerRow" dxfId="9"/>
       <tableStyleElement type="totalRow" dxfId="8"/>
       <tableStyleElement type="firstRowStripe" dxfId="7"/>
@@ -1750,6 +1739,11 @@
       <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -2032,15 +2026,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D444"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -2055,8 +2048,8 @@
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="3"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="3"/>
@@ -2656,7 +2649,7 @@
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
-      <c r="D102" s="14"/>
+      <c r="D102" s="11"/>
     </row>
     <row r="103" ht="22.05" customHeight="1" spans="1:4">
       <c r="A103" s="3"/>
@@ -4717,19 +4710,19 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="7" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="21.5535714285714" customWidth="1"/>
+    <col min="2" max="2" width="21.5555555555556" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4743,10 +4736,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="C2" s="2">
         <v>470</v>
@@ -4757,10 +4750,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="C3" s="2">
         <v>180</v>
@@ -4771,10 +4764,10 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="C4" s="2">
         <v>840</v>
@@ -4785,10 +4778,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="C5" s="2">
         <v>3000</v>
@@ -4799,10 +4792,10 @@
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="C6" s="2">
         <v>380</v>
@@ -4813,10 +4806,10 @@
     </row>
     <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>80</v>
       </c>
       <c r="C7" s="2">
         <v>290</v>
@@ -4827,10 +4820,10 @@
     </row>
     <row r="8" ht="22.05" customHeight="1" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C8" s="2">
         <v>330</v>
@@ -4846,10 +4839,10 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -4857,7 +4850,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4876,10 +4869,10 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -4887,7 +4880,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4906,10 +4899,10 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -4917,7 +4910,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4936,51 +4929,56 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="7"/>
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="20.1071428571429" customWidth="1"/>
+    <col min="1" max="1" width="20.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.4" spans="1:1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4991,14 +4989,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D27"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="26.8214285714286" customWidth="1"/>
-    <col min="2" max="2" width="13.5803571428571" customWidth="1"/>
-    <col min="3" max="4" width="12.8660714285714" customWidth="1"/>
+    <col min="1" max="1" width="26.8240740740741" customWidth="1"/>
+    <col min="2" max="2" width="13.5833333333333" customWidth="1"/>
+    <col min="3" max="4" width="12.8703703703704" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1" spans="1:4">
@@ -5268,11 +5266,11 @@
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1" spans="1:4">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="11" t="s">
-        <v>28</v>
+      <c r="B20" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="C20" s="9">
         <v>975</v>
@@ -5282,11 +5280,11 @@
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1" spans="1:4">
-      <c r="A21" s="12" t="s">
-        <v>29</v>
+      <c r="A21" s="7" t="s">
+        <v>28</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C21" s="9">
         <v>1440</v>
@@ -5296,11 +5294,11 @@
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1" spans="1:4">
-      <c r="A22" s="10" t="s">
-        <v>31</v>
+      <c r="A22" s="9" t="s">
+        <v>29</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C22" s="9">
         <v>1440</v>
@@ -5311,10 +5309,10 @@
     </row>
     <row r="23" ht="22.5" customHeight="1" spans="1:4">
       <c r="A23" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C23" s="9">
         <v>1800</v>
@@ -5325,10 +5323,10 @@
     </row>
     <row r="24" ht="22.5" customHeight="1" spans="1:4">
       <c r="A24" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C24" s="9">
         <v>1900</v>
@@ -5339,10 +5337,10 @@
     </row>
     <row r="25" ht="22.5" customHeight="1" spans="1:4">
       <c r="A25" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C25" s="9">
         <v>1960</v>
@@ -5353,10 +5351,10 @@
     </row>
     <row r="26" ht="22.5" customHeight="1" spans="1:4">
       <c r="A26" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C26" s="9">
         <v>1960</v>
@@ -5367,10 +5365,10 @@
     </row>
     <row r="27" ht="22.5" customHeight="1" spans="1:4">
       <c r="A27" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C27" s="9">
         <v>5350</v>
@@ -5386,19 +5384,19 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="3" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="44.5535714285714" customWidth="1"/>
-    <col min="2" max="2" width="34.7767857142857" customWidth="1"/>
+    <col min="1" max="1" width="44.5555555555556" customWidth="1"/>
+    <col min="2" max="2" width="34.7777777777778" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -5412,10 +5410,10 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>39</v>
       </c>
       <c r="C2" s="3">
         <v>1360</v>
@@ -5426,10 +5424,10 @@
     </row>
     <row r="3" ht="21" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="C3" s="3">
         <v>1390</v>
@@ -5440,10 +5438,10 @@
     </row>
     <row r="4" ht="21" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C4" s="3">
         <v>1340</v>
@@ -5459,10 +5457,10 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D167"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -5470,7 +5468,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -5484,10 +5482,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="C2" s="3">
         <v>870</v>
@@ -5498,10 +5496,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C3" s="2">
         <v>600</v>
@@ -6501,10 +6499,10 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -6512,7 +6510,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -6531,19 +6529,19 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="2" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="36.7767857142857" customWidth="1"/>
-    <col min="2" max="2" width="25.7767857142857" customWidth="1"/>
+    <col min="1" max="1" width="36.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="25.7777777777778" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -6557,10 +6555,10 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="C2" s="3">
         <v>2300</v>
@@ -6571,10 +6569,10 @@
     </row>
     <row r="3" ht="21" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="C3" s="3">
         <v>1860</v>
@@ -6590,10 +6588,10 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -6601,7 +6599,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -6615,10 +6613,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="C2" s="3">
         <v>350</v>
@@ -6629,10 +6627,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="C3" s="2">
         <v>3430</v>
@@ -6643,10 +6641,10 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="C4" s="3">
         <v>1000</v>
@@ -6657,10 +6655,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C5" s="2">
         <v>1120</v>
@@ -6671,10 +6669,10 @@
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="C6" s="2">
         <v>1730</v>
@@ -6685,10 +6683,10 @@
     </row>
     <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C7" s="2">
         <v>1590</v>
@@ -6699,10 +6697,10 @@
     </row>
     <row r="8" ht="22.05" customHeight="1" spans="1:4">
       <c r="A8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="C8" s="2">
         <v>1350</v>
@@ -6713,10 +6711,10 @@
     </row>
     <row r="9" ht="22.05" customHeight="1" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C9" s="2">
         <v>620</v>
@@ -6727,10 +6725,10 @@
     </row>
     <row r="10" ht="22.05" customHeight="1" spans="1:4">
       <c r="A10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="C10" s="2">
         <v>735</v>
@@ -6741,10 +6739,10 @@
     </row>
     <row r="11" ht="22.05" customHeight="1" spans="1:4">
       <c r="A11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="C11" s="2">
         <v>780</v>
@@ -6760,10 +6758,10 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -6771,7 +6769,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -6790,10 +6788,10 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="2" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -6801,7 +6799,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -6813,12 +6811,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="15.4" spans="1:4">
+    <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C2" s="4">
         <v>3350</v>
@@ -6827,12 +6825,12 @@
         <v>3350</v>
       </c>
     </row>
-    <row r="3" ht="15.4" spans="1:4">
+    <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C3" s="4">
         <v>3200</v>
